--- a/Result/profitability/1712.xlsx
+++ b/Result/profitability/1712.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.59875</v>
+        <v>0.63625</v>
       </c>
       <c r="N2" t="n">
-        <v>29.84</v>
+        <v>30.05</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5912500000000001</v>
+        <v>0.6312500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>29.5275</v>
+        <v>30.01</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.27</v>
       </c>
       <c r="M4" t="n">
-        <v>0.555</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>29.145</v>
+        <v>29.25875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.08</v>
       </c>
       <c r="M5" t="n">
-        <v>0.445</v>
+        <v>0.4662500000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>28.39375</v>
+        <v>28.62875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.4</v>
       </c>
       <c r="M6" t="n">
-        <v>0.4062500000000001</v>
+        <v>0.44625</v>
       </c>
       <c r="N6" t="n">
-        <v>28.17625</v>
+        <v>28.33375</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.36375</v>
+        <v>0.4075</v>
       </c>
       <c r="N7" t="n">
-        <v>27.57375</v>
+        <v>27.95125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3225</v>
+        <v>0.34875</v>
       </c>
       <c r="N8" t="n">
-        <v>27.23625</v>
+        <v>27.4325</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1712</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5374</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3641</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1732</v>
+      </c>
+      <c r="F75" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="G75" t="n">
+        <v>472</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>467</v>
+      </c>
+      <c r="K75" t="n">
+        <v>371</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.66125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>30.4675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3134328358208955</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.05119008803390934</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.23943661971831</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.880000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.06192358366271411</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
